--- a/config/配置_英博_储能柜.xlsx
+++ b/config/配置_英博_储能柜.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -54,10 +54,10 @@
     <t>project</t>
   </si>
   <si>
-    <t>英博自研</t>
-  </si>
-  <si>
-    <t>项目名称：</t>
+    <t>英博自研电池管理系统</t>
+  </si>
+  <si>
+    <t>项目名称</t>
   </si>
   <si>
     <t>feature</t>
@@ -309,7 +309,7 @@
     <t>ModbusTCP</t>
   </si>
   <si>
-    <t>./config/PCS_125_英博.xlsx</t>
+    <t>./config/pcs/PCS_英博_125.xlsx</t>
   </si>
   <si>
     <t>192.168.0.20</t>
@@ -318,7 +318,7 @@
     <t>CAN</t>
   </si>
   <si>
-    <t>./config/永泰_2_BCU.xlsx</t>
+    <t>./config/bms/BCU_永泰.xlsx</t>
   </si>
   <si>
     <t>can0</t>
@@ -327,7 +327,7 @@
     <t>ModbusRTU</t>
   </si>
   <si>
-    <t>./config/除湿机.xlsx</t>
+    <t>./config/辅控/除湿机.xlsx</t>
   </si>
   <si>
     <t>/dev/ttyXRUSB1</t>
@@ -336,19 +336,19 @@
     <t>N</t>
   </si>
   <si>
-    <t>./config/水冷机组_埃森特.xlsx</t>
+    <t>./config/液冷机组/水冷机组_埃森特.xlsx</t>
   </si>
   <si>
     <t>/dev/ttyXRUSB3</t>
   </si>
   <si>
-    <t>./config/消防温感烟感.xlsx</t>
+    <t>./config/辅控/消防温感烟感.xlsx</t>
   </si>
   <si>
     <t>/dev/ttyXRUSB2</t>
   </si>
   <si>
-    <t>./config/GPIO.xlsx</t>
+    <t>./config/gpio/GPIO.xlsx</t>
   </si>
   <si>
     <t>device_id</t>
@@ -1003,7 +1003,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1016,19 +1016,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1345,9 +1336,9 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="22.4047619047619" style="4"/>
-    <col min="2" max="2" width="33.7936507936508" style="4" customWidth="1"/>
-    <col min="3" max="16384" width="22.4047619047619" style="4"/>
+    <col min="1" max="1" width="22.4047619047619" style="2"/>
+    <col min="2" max="2" width="33.7936507936508" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="22.4047619047619" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1362,24 +1353,24 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1396,16 +1387,16 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="17.5238095238095" style="7" customWidth="1"/>
-    <col min="2" max="2" width="19.0079365079365" style="7" customWidth="1"/>
-    <col min="3" max="3" width="31.1825396825397" style="7" customWidth="1"/>
-    <col min="4" max="4" width="19.1428571428571" style="7" customWidth="1"/>
-    <col min="5" max="6" width="10.4206349206349" style="7" customWidth="1"/>
-    <col min="7" max="7" width="20.6666666666667" style="7" customWidth="1"/>
-    <col min="8" max="16384" width="9.03174603174603" style="7"/>
+    <col min="1" max="1" width="17.5238095238095" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.0079365079365" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.1825396825397" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1428571428571" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.4206349206349" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.03174603174603" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1428,190 +1419,190 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="1" spans="1:7">
-      <c r="A2" s="4" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="8" t="b">
+      <c r="F2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" s="8" customFormat="1" spans="1:7">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="8" t="b">
+      <c r="F3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" spans="1:7">
-      <c r="B4" s="4" t="s">
+    <row r="4" s="2" customFormat="1" spans="1:7">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="2">
         <v>9091</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" s="8" customFormat="1" spans="1:7">
-      <c r="A5" s="4" t="s">
+    <row r="5" s="2" customFormat="1" spans="1:7">
+      <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="8" t="b">
+      <c r="F5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" s="8" customFormat="1" spans="1:7">
-      <c r="A6" s="4" t="s">
+    <row r="6" s="2" customFormat="1" spans="1:7">
+      <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="8" t="b">
+      <c r="F6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" s="8" customFormat="1" spans="1:7">
-      <c r="B7" s="4" t="s">
+    <row r="7" s="2" customFormat="1" spans="1:7">
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>9092</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" s="8" customFormat="1" spans="1:7">
-      <c r="B8" s="4" t="s">
+    <row r="8" s="2" customFormat="1" spans="1:7">
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" s="8" customFormat="1" spans="1:7">
-      <c r="A9" s="4" t="s">
+    <row r="9" s="2" customFormat="1" spans="1:7">
+      <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="8" t="b">
+      <c r="F9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" s="8" customFormat="1" spans="1:7">
-      <c r="A10" s="4" t="s">
+    <row r="10" s="2" customFormat="1" spans="1:7">
+      <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="8" t="b">
+      <c r="F10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" s="8" customFormat="1" spans="1:7">
-      <c r="B11" s="4" t="s">
+    <row r="11" s="2" customFormat="1" spans="1:7">
+      <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>1883</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" s="8" customFormat="1" spans="1:7">
-      <c r="B12" s="4" t="s">
+    <row r="12" s="2" customFormat="1" spans="1:7">
+      <c r="B12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" s="8" customFormat="1" spans="1:7">
-      <c r="B13" s="4" t="s">
+    <row r="13" s="2" customFormat="1" spans="1:7">
+      <c r="B13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" s="8" customFormat="1" spans="1:7">
-      <c r="B14" s="4" t="s">
+    <row r="14" s="2" customFormat="1" spans="1:7">
+      <c r="B14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" s="8" customFormat="1" spans="1:7">
-      <c r="B15" s="4" t="s">
+    <row r="15" s="2" customFormat="1" spans="1:7">
+      <c r="B15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1638,11 +1629,11 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="6.46031746031746" style="4" customWidth="1"/>
-    <col min="2" max="2" width="20.9285714285714" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.3333333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.5396825396825" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.9285714285714" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.3333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.5396825396825" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:5">
@@ -1658,89 +1649,89 @@
       <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="4"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1757,17 +1748,17 @@
   <dimension ref="A1:S7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="6.46031746031746" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.5952380952381" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.4603174603175" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.9285714285714" style="4" customWidth="1"/>
-    <col min="5" max="5" width="44.531746031746" style="4" customWidth="1"/>
-    <col min="6" max="10" width="12.1984126984127" style="4" customWidth="1"/>
-    <col min="11" max="11" width="16.6666666666667" style="4" customWidth="1"/>
-    <col min="12" max="16" width="12.1984126984127" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.07142857142857" style="4"/>
-    <col min="18" max="18" width="15.2142857142857" style="4" customWidth="1"/>
-    <col min="19" max="16384" width="9.07142857142857" style="4"/>
+    <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.5952380952381" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.4603174603175" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.9285714285714" style="2" customWidth="1"/>
+    <col min="5" max="5" width="44.531746031746" style="2" customWidth="1"/>
+    <col min="6" max="10" width="12.1984126984127" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.6666666666667" style="2" customWidth="1"/>
+    <col min="12" max="16" width="12.1984126984127" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.07142857142857" style="2"/>
+    <col min="18" max="18" width="15.2142857142857" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9.07142857142857" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:19">
@@ -1801,22 +1792,22 @@
       <c r="J1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>88</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -1830,212 +1821,212 @@
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="4">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>1000</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="2">
         <v>2000</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="2">
         <v>502</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>2000</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="2">
         <v>5000</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="L3" s="4">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="L3" s="2">
         <v>500000</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="2" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>2000</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="2">
         <v>2000</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="2">
         <v>2</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="2">
         <v>9600</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="2">
         <v>8</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>2000</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="2">
         <v>2000</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="2">
         <v>1</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="2">
         <v>9600</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="2">
         <v>8</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>2000</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="2">
         <v>2000</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="2">
         <v>1</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="2">
         <v>9600</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="2">
         <v>8</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>2000</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="2">
         <v>2000</v>
       </c>
     </row>
